--- a/artfynd/Maskaure Myrås avvanm, 5 ha artfynd.xlsx
+++ b/artfynd/Maskaure Myrås avvanm, 5 ha artfynd.xlsx
@@ -5281,7 +5281,7 @@
         <v>135336954</v>
       </c>
       <c r="B42" t="n">
-        <v>57980</v>
+        <v>58008</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5307,11 +5307,14 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Myrås, Pi lm</t>
@@ -5402,7 +5405,7 @@
         <v>135336955</v>
       </c>
       <c r="B43" t="n">
-        <v>57980</v>
+        <v>58008</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5428,11 +5431,14 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Myrås, Pi lm</t>
@@ -5523,7 +5529,7 @@
         <v>135336960</v>
       </c>
       <c r="B44" t="n">
-        <v>57980</v>
+        <v>58008</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5644,7 +5650,7 @@
         <v>135336965</v>
       </c>
       <c r="B45" t="n">
-        <v>57980</v>
+        <v>58008</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5670,11 +5676,14 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Myrås, Pi lm</t>

--- a/artfynd/Maskaure Myrås avvanm, 5 ha artfynd.xlsx
+++ b/artfynd/Maskaure Myrås avvanm, 5 ha artfynd.xlsx
@@ -5281,7 +5281,7 @@
         <v>135336954</v>
       </c>
       <c r="B42" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>135336955</v>
       </c>
       <c r="B43" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>135336960</v>
       </c>
       <c r="B44" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>135336965</v>
       </c>
       <c r="B45" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/Maskaure Myrås avvanm, 5 ha artfynd.xlsx
+++ b/artfynd/Maskaure Myrås avvanm, 5 ha artfynd.xlsx
@@ -5281,7 +5281,7 @@
         <v>135336954</v>
       </c>
       <c r="B42" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>135336955</v>
       </c>
       <c r="B43" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>135336960</v>
       </c>
       <c r="B44" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>135336965</v>
       </c>
       <c r="B45" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/Maskaure Myrås avvanm, 5 ha artfynd.xlsx
+++ b/artfynd/Maskaure Myrås avvanm, 5 ha artfynd.xlsx
@@ -5309,11 +5309,7 @@
       <c r="I42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5433,11 +5429,7 @@
       <c r="I43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5555,11 +5547,7 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Myrås, Pi lm</t>
@@ -5678,11 +5666,7 @@
       <c r="I45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>

--- a/artfynd/Maskaure Myrås avvanm, 5 ha artfynd.xlsx
+++ b/artfynd/Maskaure Myrås avvanm, 5 ha artfynd.xlsx
@@ -5281,7 +5281,7 @@
         <v>135336954</v>
       </c>
       <c r="B42" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
         <v>135336955</v>
       </c>
       <c r="B43" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5521,7 +5521,7 @@
         <v>135336960</v>
       </c>
       <c r="B44" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         <v>135336965</v>
       </c>
       <c r="B45" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/Maskaure Myrås avvanm, 5 ha artfynd.xlsx
+++ b/artfynd/Maskaure Myrås avvanm, 5 ha artfynd.xlsx
@@ -5281,7 +5281,7 @@
         <v>135336954</v>
       </c>
       <c r="B42" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
         <v>135336955</v>
       </c>
       <c r="B43" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5521,7 +5521,7 @@
         <v>135336960</v>
       </c>
       <c r="B44" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         <v>135336965</v>
       </c>
       <c r="B45" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/Maskaure Myrås avvanm, 5 ha artfynd.xlsx
+++ b/artfynd/Maskaure Myrås avvanm, 5 ha artfynd.xlsx
@@ -5281,7 +5281,7 @@
         <v>135336954</v>
       </c>
       <c r="B42" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
         <v>135336955</v>
       </c>
       <c r="B43" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5521,7 +5521,7 @@
         <v>135336960</v>
       </c>
       <c r="B44" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         <v>135336965</v>
       </c>
       <c r="B45" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
